--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104752_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104752_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1446</v>
+        <v>3.2036</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5336</v>
+        <v>2.7181</v>
       </c>
       <c r="F2" t="n">
-        <v>0.611</v>
+        <v>0.4855</v>
       </c>
       <c r="G2" t="n">
         <v>1.4198</v>
@@ -610,13 +610,13 @@
         <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.9973</v>
+        <v>-0.9383</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8179</v>
+        <v>0.3665</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1794</v>
+        <v>-1.3049</v>
       </c>
       <c r="V2" t="n">
         <v>2.4945</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2461</v>
+        <v>2.1241</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5876</v>
+        <v>2.9054</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3415</v>
+        <v>-0.7813</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4888</v>
+        <v>1.2751</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4852</v>
+        <v>0.8013</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9964</v>
+        <v>0.4738</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3712</v>
+        <v>2.5061</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1828</v>
+        <v>1.4339</v>
       </c>
       <c r="L3" t="n">
-        <v>2.554</v>
+        <v>1.0722</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8599</v>
+        <v>-1.231</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3023</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5576</v>
+        <v>-0.5984</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8211</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8211</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.244</v>
+        <v>-0.4681</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0587</v>
+        <v>0.448</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3027</v>
+        <v>-0.916</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1578</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1578</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2009</v>
+        <v>1.1741</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0763</v>
+        <v>2.4635</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8754</v>
+        <v>-1.2894</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2751</v>
+        <v>1.311</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8013</v>
+        <v>1.4703</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4738</v>
+        <v>-0.1592</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5061</v>
+        <v>1.9248</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4339</v>
+        <v>1.4856</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0722</v>
+        <v>0.4392</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.231</v>
+        <v>-0.6138</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.0154</v>
       </c>
       <c r="O4" t="n">
         <v>-0.5984</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2276</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3658</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3913</v>
+        <v>-1.0475</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3812</v>
+        <v>0.5874</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0101</v>
+        <v>-1.6349</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7987</v>
+        <v>1.1226</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6446</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.846</v>
+        <v>-1.8773</v>
       </c>
       <c r="G5" t="n">
         <v>1.2422</v>
@@ -844,13 +844,13 @@
         <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.354</v>
+        <v>-1.0301</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4182</v>
+        <v>-0.0629</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9358</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5678</v>
+        <v>0.3786</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1081</v>
+        <v>1.877</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5403</v>
+        <v>-1.4984</v>
       </c>
       <c r="G6" t="n">
-        <v>1.311</v>
+        <v>-0.4888</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4703</v>
+        <v>-1.4852</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1592</v>
+        <v>0.9964</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9248</v>
+        <v>1.3712</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4856</v>
+        <v>-1.1828</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4392</v>
+        <v>2.554</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6138</v>
+        <v>-1.8599</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0154</v>
+        <v>-0.3023</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5984</v>
+        <v>-1.5576</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9105</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0487</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6538</v>
+        <v>-1.1115</v>
       </c>
       <c r="T6" t="n">
-        <v>0.232</v>
+        <v>0.348</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.8858</v>
+        <v>-1.4595</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0895</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1847</v>
+        <v>-1.1707</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7911</v>
+        <v>2.5542</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9758</v>
+        <v>-3.7249</v>
       </c>
       <c r="G7" t="n">
         <v>0.2766</v>
@@ -1000,13 +1000,13 @@
         <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5994</v>
+        <v>-0.5854</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0468</v>
+        <v>-0.2837</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5527</v>
+        <v>-0.3017</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0895</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>A. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9681</v>
+        <v>-2.7979</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1127</v>
+        <v>-1.2472</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8554</v>
+        <v>-1.5506</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4511</v>
+        <v>-3.5315</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2802</v>
+        <v>-1.1484</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1708</v>
+        <v>-2.3832</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5648</v>
+        <v>-0.9702</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6765</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1117</v>
+        <v>-0.2388</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8863</v>
+        <v>-2.5613</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6037</v>
+        <v>-0.4169</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2826</v>
+        <v>-2.1444</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.1868</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.5526</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
         <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2145</v>
+        <v>0.3483</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5997</v>
+        <v>0.7034</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3852</v>
+        <v>-0.3551</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5447</v>
+        <v>0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>1.405</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.9497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3798</v>
+        <v>-3.0099</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8919</v>
+        <v>-2.1136</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4879</v>
+        <v>-0.8963</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5315</v>
+        <v>-1.6293</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1484</v>
+        <v>-0.7729</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3832</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9702</v>
+        <v>-0.8428</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.6862</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2388</v>
+        <v>-0.1566</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5613</v>
+        <v>-0.7865</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4169</v>
+        <v>-0.0866</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1444</v>
+        <v>-0.6998</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2276</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3658</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7663</v>
+        <v>-0.54</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0587</v>
+        <v>-0.1326</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2924</v>
+        <v>-0.4074</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1578</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0202</v>
+        <v>-3.9957</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4689</v>
+        <v>-1.8894</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5513</v>
+        <v>-2.1064</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6293</v>
+        <v>-1.4511</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7729</v>
+        <v>-1.2802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.1708</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8428</v>
+        <v>-0.5648</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6862</v>
+        <v>-0.6765</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1566</v>
+        <v>0.1117</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7865</v>
+        <v>-0.8863</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0866</v>
+        <v>-0.6037</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6998</v>
+        <v>-0.2826</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6829</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1382</v>
+        <v>-4.5526</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4553</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5503</v>
+        <v>1.1869</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4879</v>
+        <v>1.823</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0623</v>
+        <v>-0.6361</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1578</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1578</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.4054</v>
+        <v>-7.5168</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2602</v>
+        <v>-3.4971</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.1452</v>
+        <v>-4.0197</v>
       </c>
       <c r="G11" t="n">
         <v>-5.4354</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2089</v>
+        <v>0.0975</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5991</v>
+        <v>0.3622</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3901</v>
+        <v>-0.2647</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1789</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.825699999999999</v>
+        <v>-8.446199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6819</v>
+        <v>-3.3262</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.1438</v>
+        <v>-5.12</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8779</v>
+        <v>-4.8014</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.859</v>
+        <v>-2.7546</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0188</v>
+        <v>-2.0467</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1693</v>
+        <v>-0.0017</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3555</v>
+        <v>-1.4759</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1862</v>
+        <v>1.4741</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.7086</v>
+        <v>-4.7996</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5036</v>
+        <v>-1.2788</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.205</v>
+        <v>-3.5209</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.5039</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q12" t="n">
         <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9105</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5122</v>
+        <v>-0.5263</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2559</v>
+        <v>-0.0678</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2563</v>
+        <v>-0.4586</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9317</v>
+        <v>-0.387</v>
       </c>
       <c r="W12" t="n">
         <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0895</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.1953</v>
+        <v>-9.0869</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9184</v>
+        <v>-4.0372</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.2769</v>
+        <v>-5.0497</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.8014</v>
+        <v>-3.8779</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7546</v>
+        <v>-0.859</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.0467</v>
+        <v>-3.0188</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0017</v>
+        <v>-0.1693</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4759</v>
+        <v>-0.3555</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4741</v>
+        <v>0.1862</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.7996</v>
+        <v>-3.7086</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2788</v>
+        <v>-0.5036</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.5209</v>
+        <v>-3.205</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.7316</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q13" t="n">
         <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6829</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2754</v>
+        <v>-1.7734</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.66</v>
+        <v>-0.6112</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-1.1622</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.387</v>
+        <v>-0.9317</v>
       </c>
       <c r="W13" t="n">
         <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5447</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1504,7 +1504,7 @@
         <v>-28.0211</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5926999999999993</v>
+        <v>-0.5925000000000011</v>
       </c>
       <c r="F14" t="n">
         <v>-27.4285</v>
@@ -1519,13 +1519,13 @@
         <v>-9.8743</v>
       </c>
       <c r="J14" t="n">
-        <v>7.428199999999998</v>
+        <v>7.428199999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6541999999999992</v>
+        <v>0.6542000000000003</v>
       </c>
       <c r="L14" t="n">
-        <v>6.773700000000001</v>
+        <v>6.773699999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-23.1187</v>
@@ -1546,13 +1546,13 @@
         <v>13.6579</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.388000000000001</v>
+        <v>-6.3879</v>
       </c>
       <c r="T14" t="n">
         <v>3.4803</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.8682</v>
+        <v>-9.868300000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.39</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7003</v>
+        <v>11.5051</v>
       </c>
       <c r="E15" t="n">
-        <v>9.6388</v>
+        <v>10.3494</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0615</v>
+        <v>1.1556</v>
       </c>
       <c r="G15" t="n">
         <v>8.4297</v>
@@ -1624,13 +1624,13 @@
         <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.043</v>
+        <v>1.8477</v>
       </c>
       <c r="T15" t="n">
-        <v>0.757</v>
+        <v>1.4677</v>
       </c>
       <c r="U15" t="n">
-        <v>0.286</v>
+        <v>0.3801</v>
       </c>
       <c r="V15" t="n">
         <v>0.5447</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9456</v>
+        <v>6.8483</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2337</v>
+        <v>5.1677</v>
       </c>
       <c r="F16" t="n">
-        <v>1.712</v>
+        <v>1.6806</v>
       </c>
       <c r="G16" t="n">
         <v>3.5862</v>
@@ -1702,13 +1702,13 @@
         <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0636</v>
+        <v>1.9662</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9865</v>
+        <v>1.9205</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0771</v>
+        <v>0.0457</v>
       </c>
       <c r="V16" t="n">
         <v>0.1578</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.1785</v>
+        <v>6.0693</v>
       </c>
       <c r="E17" t="n">
-        <v>5.0474</v>
+        <v>4.8105</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1311</v>
+        <v>1.2588</v>
       </c>
       <c r="G17" t="n">
         <v>5.1002</v>
@@ -1780,13 +1780,13 @@
         <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9386</v>
+        <v>0.8294</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6176</v>
+        <v>0.3807</v>
       </c>
       <c r="U17" t="n">
-        <v>0.321</v>
+        <v>0.4487</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3155</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2937</v>
+        <v>5.5945</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5867</v>
+        <v>4.3013</v>
       </c>
       <c r="F18" t="n">
-        <v>0.707</v>
+        <v>1.2932</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9814000000000001</v>
+        <v>5.8698</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9275</v>
+        <v>4.6819</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0539</v>
+        <v>1.1878</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9506</v>
+        <v>5.7953</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7272</v>
+        <v>4.3814</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2234</v>
+        <v>1.4139</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0308</v>
+        <v>0.0745</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2003</v>
+        <v>0.3005</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1695</v>
+        <v>-0.226</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5934</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5934</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7189</v>
+        <v>-0.0476</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5466</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1723</v>
+        <v>-1.0576</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7259</v>
+        <v>4.0498</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9984</v>
+        <v>3.4683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7275</v>
+        <v>0.5815</v>
       </c>
       <c r="G19" t="n">
-        <v>5.8698</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6819</v>
+        <v>0.9275</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1878</v>
+        <v>0.0539</v>
       </c>
       <c r="J19" t="n">
-        <v>5.7953</v>
+        <v>0.9506</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3814</v>
+        <v>0.7272</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4139</v>
+        <v>0.2234</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0745</v>
+        <v>0.0308</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3005</v>
+        <v>0.2003</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.226</v>
+        <v>-0.1695</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2276</v>
+        <v>1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5039</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2763</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9162</v>
+        <v>1.475</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2929</v>
+        <v>1.4282</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6233</v>
+        <v>0.0468</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.6767</v>
+        <v>3.2889</v>
       </c>
       <c r="E20" t="n">
-        <v>4.4402</v>
+        <v>3.6111</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7635</v>
+        <v>-0.3222</v>
       </c>
       <c r="G20" t="n">
         <v>1.6045</v>
@@ -2014,13 +2014,13 @@
         <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0997</v>
+        <v>1.7119</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2666</v>
+        <v>1.4374</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1669</v>
+        <v>0.2744</v>
       </c>
       <c r="V20" t="n">
         <v>2.0212</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2507</v>
+        <v>0.8105</v>
       </c>
       <c r="E21" t="n">
-        <v>0.759</v>
+        <v>0.8774</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5083</v>
+        <v>-0.067</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2198</v>
@@ -2092,13 +2092,13 @@
         <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9848</v>
+        <v>-0.425</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3115</v>
+        <v>-0.193</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6733</v>
+        <v>-0.232</v>
       </c>
       <c r="V21" t="n">
         <v>1.0895</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0411</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2345</v>
+        <v>0.1431</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1598</v>
+        <v>-0.102</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.346</v>
+        <v>-0.8555</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3501</v>
+        <v>-0.2674</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0041</v>
+        <v>-0.5881</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2998</v>
+        <v>-0.0402</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4449</v>
+        <v>-0.1519</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7447</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6458</v>
+        <v>-0.8154</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9052</v>
+        <v>-0.1155</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2593</v>
+        <v>-0.6998</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6829</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3658</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6829</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4192</v>
+        <v>-0.0139</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3005</v>
+        <v>0.1833</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1187</v>
+        <v>-0.1972</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5674</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2122</v>
+        <v>-0.2393</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3551</v>
+        <v>-0.3166</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8555</v>
+        <v>-0.346</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2674</v>
+        <v>-1.3501</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5881</v>
+        <v>1.0041</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0402</v>
+        <v>0.2998</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1519</v>
+        <v>-0.4449</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1117</v>
+        <v>0.7447</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8154</v>
+        <v>-0.6458</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1155</v>
+        <v>-0.9052</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6998</v>
+        <v>0.2593</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9105</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9105</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6224</v>
+        <v>0.7885</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1721</v>
+        <v>0.8267</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4503</v>
+        <v>-0.0381</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.841</v>
+        <v>-1.6982</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.961</v>
+        <v>-0.7241</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.88</v>
+        <v>-0.9741</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9676</v>
@@ -2326,13 +2326,13 @@
         <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2392</v>
+        <v>-0.0964</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2091</v>
+        <v>0.0278</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0301</v>
+        <v>-0.1242</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0895</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7514</v>
+        <v>-1.7817</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0838</v>
+        <v>-2.4915</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3323</v>
+        <v>0.7098</v>
       </c>
       <c r="G25" t="n">
         <v>-3.2546</v>
@@ -2404,13 +2404,13 @@
         <v>2.5039</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2009</v>
+        <v>-0.2312</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1994</v>
+        <v>0.7916</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4002</v>
+        <v>-1.0228</v>
       </c>
       <c r="V25" t="n">
         <v>1.4764</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.6652</v>
+        <v>-4.5711</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2531</v>
+        <v>-1.8453</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4122</v>
+        <v>-2.7258</v>
       </c>
       <c r="G26" t="n">
         <v>-3.2376</v>
@@ -2482,13 +2482,13 @@
         <v>0.9105</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0685</v>
+        <v>0.1626</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1796</v>
+        <v>0.5874</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1111</v>
+        <v>-0.4248</v>
       </c>
       <c r="V26" t="n">
         <v>-2.1789</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>28.0212</v>
+        <v>29.6006</v>
       </c>
       <c r="E27" t="n">
         <v>27.4286</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5925000000000002</v>
+        <v>2.171799999999999</v>
       </c>
       <c r="G27" t="n">
         <v>15.6907</v>
       </c>
       <c r="H27" t="n">
-        <v>5.8161</v>
+        <v>5.816100000000001</v>
       </c>
       <c r="I27" t="n">
         <v>9.874199999999998</v>
@@ -2539,16 +2539,16 @@
         <v>6.4706</v>
       </c>
       <c r="L27" t="n">
-        <v>16.648</v>
+        <v>16.64800000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-7.428100000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.6543000000000001</v>
+        <v>-0.6542999999999998</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.7738</v>
+        <v>-6.773800000000001</v>
       </c>
       <c r="P27" t="n">
         <v>4.552699999999999</v>
@@ -2560,13 +2560,13 @@
         <v>18.2104</v>
       </c>
       <c r="S27" t="n">
-        <v>6.388000000000001</v>
+        <v>7.967200000000002</v>
       </c>
       <c r="T27" t="n">
-        <v>9.868200000000002</v>
+        <v>9.868300000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.4801</v>
+        <v>-1.901</v>
       </c>
       <c r="V27" t="n">
         <v>1.3902</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104752_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104752_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.099600000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104752_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.7094</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
